--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -467,6 +474,32 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>European Southern Observatory</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sustainability Procurement Advisor</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>...are located in Garching, near Munich, Germany. At Paranal, ESO ope...</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://recruitment.eso.org/jobs/2026_0041</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,32 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>European Southern Observatory</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Sustainability Procurement Advisor</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>...are located in Garching, near Munich, Germany. At Paranal, ESO ope...</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>https://recruitment.eso.org/jobs/2026_0041</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -467,6 +474,66 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Product Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2698687</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -475,60 +475,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Tanso</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Associate Sustainability Specialist (f/m/x)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://tanso.jobs.personio.de/job/2644410</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Tanso</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>(Senior) Product Sustainability Specialist (f/m/x)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://tanso.jobs.personio.de/job/2698687</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,66 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tanso</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Associate Sustainability Specialist (f/m/x)</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://tanso.jobs.personio.de/job/2644410</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tanso</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(Senior) Product Sustainability Specialist (f/m/x)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://tanso.jobs.personio.de/job/2698687</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -467,6 +474,144 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Start-up Intelligence Circular Economy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2723225</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CSR Jobs in München</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>CSR Jobs in München | NachhaltigeJobs Nachhaltige...</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nachhaltigkeit</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/nachhaltigkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,140 +475,163 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Werkstudent_in (m/w/d) Start-up Intelligence Circular Economy</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2723225</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Tanso</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Associate Sustainability Specialist (f/m/x)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://tanso.jobs.personio.de/job/2644410</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>NachhaltigeJobs.de (Munich)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>CSR Jobs in München</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>CSR Jobs in München | NachhaltigeJobs Nachhaltige...</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Michael Page Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Nachhaltigkeit</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/jobs/nachhaltigkeit</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>NachhaltigeJobs.de (Munich)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Umwelt Jobs in München</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Roles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Sustainability (Europe)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +43,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,164 +469,111 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>UnternehmerTUM</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Werkstudent_in (m/w/d) Start-up Intelligence Circular Economy</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>München Kreativquartier</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2723225</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Job Posted</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance Score (1-10)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tanso</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Associate Sustainability Specialist (f/m/x)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://tanso.jobs.personio.de/job/2644410</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NachhaltigeJobs.de (Munich)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CSR Jobs in München</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CSR Jobs in München | NachhaltigeJobs Nachhaltige...</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Michael Page Germany (Nachhaltigkeit)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nachhaltigkeit</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/jobs/nachhaltigkeit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NachhaltigeJobs.de (Munich)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Umwelt Jobs in München</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>BUND Naturschutz in Bayern</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Job Posted</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance Score (1-10)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -469,6 +490,196 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Start-up Intelligence Circular Economy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2723225</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CSR Jobs in München</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>CSR Jobs in München | NachhaltigeJobs Nachhaltige...</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nachhaltigkeit</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/nachhaltigkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Munich, all roles)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) im Bereich Nachhaltigkeit</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>...im Bereich Nachhaltigkeit in München | Randstad randstad Jobsuche...</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/werkstudent-mwd-im-bereich-nachhaltigkeit_muenchen_c01304109/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -480,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,6 +734,716 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Assistant to the executive Board (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Garching</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2706851</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Community Manager (m/w/d) - Front Desk MakerSpace Garching</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Garching</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2709394</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Export (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>...rbeiter Export (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-export-wmd/06640-0013462604-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013475955-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Call Center Agent</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-dienstleistung-und-service/j-call-center-agent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Buchhaltung</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-finanz-und-rechnungswesen/t-rechnungswesen/j-sachbearbeiter-buchhaltung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Auftragssachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-marketing-und-vertrieb/t-vertrieb-und-verkauf/j-auftragssachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz der Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz-der-geschaeftsfuehrung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Bürokaufmann</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-buerokaufmann/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Empfangsmitarbeiter</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-empfangsmitarbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Personalsachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-personalwesen/j-personalsachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Projektassistenz</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektassistenz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Verwaltungsfachangestellter</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-verwaltungsfachangestellter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013471891-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Munich, all roles)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Management-Assistenz (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>...nagement-Assistenz (m/w/d) in München | Randstad randstad Jobsuche...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/management-assistenz-mwd_muenchen_c01310721/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Facility Management</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/facility-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sales Support &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/sales-support-customer-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Amadeus Fire (Munich)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Backoffice</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://karriere.amadeus-fire.de/backoffice</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz des Gesamtbetriebsrats ( w/m/d)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>...tbetriebsrats ( w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistenz-des-gesamtbetriebsrats-wmd/06604-0013483434-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013482368-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013479384-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Sekretär der Führungsebene (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>...Führungsebene (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sekretär-der-führungsebene-wmd/06604-0013471824-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Kreditsachbearbeiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>...sachbearbeiter (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/kreditsachbearbeiter-wmd/06644-0013484134-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Technische Vertriebsassistenz (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>...riebsassistenz (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/technische-vertriebsassistenz-wmd/06604-0013485530-dede</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -534,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -577,6 +1498,448 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>5 C CarbonPlan 1 job 118</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/carbonplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>6 F FirstCarbon Solutions (FCS), an ADEC Innovation 1 job 113</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/firstcarbon-solutions-fcs-an-adec-innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>ESG &amp; Carbon</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Climate Policy</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/advocacy-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2 C Climate Collective Foundation 1 job 320</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climate-collective-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>3 C Climate Action Reserve 2 jobs 164</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climateactionreserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>4 G goodcarbon 3 jobs 127</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/goodcarbon-earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>7 C ClimateWorks Foundation 2 jobs 109</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climateworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Carbon Capture and Storage (15)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Climate and Energy Analyst (27)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs Newsletter</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Why climate.jobs?</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/why-climate-jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -491,190 +491,185 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Werkstudent_in (m/w/d) Start-up Intelligence Circular Economy</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2723225</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Tanso</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Associate Sustainability Specialist (f/m/x)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://tanso.jobs.personio.de/job/2644410</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>NachhaltigeJobs.de (Munich)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>CSR Jobs in München</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>CSR Jobs in München | NachhaltigeJobs Nachhaltige...</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Michael Page Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Nachhaltigkeit</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/jobs/nachhaltigkeit</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>BUND Naturschutz in Bayern</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>NachhaltigeJobs.de (Munich)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Umwelt Jobs in München</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Randstad Germany (Munich, all roles)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Werkstudent (m/w/d) im Bereich Nachhaltigkeit</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>...im Bereich Nachhaltigkeit in München | Randstad randstad Jobsuche...</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/werkstudent-mwd-im-bereich-nachhaltigkeit_muenchen_c01304109/</t>
         </is>
@@ -691,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -737,138 +732,140 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Planet A Foods</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Office Management &amp; HR - Werkstudent (f/m/d) Food Tech Startup | 14-20h/Woche</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://planetafoods.jobs.personio.de/job/2755621</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Assistant to the executive Board (m/w/d)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D3" t="n">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Garching</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2706851</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Community Manager (m/w/d) - Front Desk MakerSpace Garching</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Garching</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2709394</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Robert Half Munich (All roles)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Sachbearbeiter Export (w/m/d)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>...rbeiter Export (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-export-wmd/06640-0013462604-dede</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Robert Half Munich (All roles)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013475955-dede</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Randstad Germany (Nachhaltigkeit)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Sachbearbeiter</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter/</t>
         </is>
       </c>
     </row>
@@ -876,25 +873,25 @@
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Randstad Germany (Nachhaltigkeit)</t>
+          <t>Robert Half Munich (Assistenz)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Call Center Agent</t>
+          <t>Assistent Personalabteilung</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+          <t>...fentlichen Dienst mit Sitz in München, zum nächstmöglichen Zeitpunk...</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>https://www.randstad.de/jobs/b-dienstleistung-und-service/j-call-center-agent/</t>
+          <t>https://www.roberthalf.com/de/de/job/deutschland/assistent-personalabteilung/06604-0013487193-dede</t>
         </is>
       </c>
     </row>
@@ -902,389 +899,375 @@
       <c r="A8" s="3" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>Tempton Personaldienstleistungen</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>12.08.2026 Personalsachbearbeiter / kaufmännischer Mitarbeiterin Lohn und Gehalt / Bürokauffrau (m/w/d) München</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>...n auf LinkedIn Jetzt bewerben München , Vollzeit Personalsachbearbe...</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tempton.de/karriere-intern/jobs/personalsachbearbeiter-kaufmaennischer-mitarbeiterin-lohn-gehalt-buerokauffrau</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Call Center Agent</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-dienstleistung-und-service/j-call-center-agent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sachbearbeiter Buchhaltung</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-finanz-und-rechnungswesen/t-rechnungswesen/j-sachbearbeiter-buchhaltung/</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Auftragssachbearbeiter</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-marketing-und-vertrieb/t-vertrieb-und-verkauf/j-auftragssachbearbeiter/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Assistenz</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Assistenz der Geschäftsführung</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz-der-geschaeftsfuehrung/</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Bürokaufmann</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-buerokaufmann/</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Empfangsmitarbeiter</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-empfangsmitarbeiter/</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Personalsachbearbeiter</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D17" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-personalwesen/j-personalsachbearbeiter/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Projektassistenz</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektassistenz/</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Sachbearbeiter</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D19" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-sachbearbeiter/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Randstad Germany (Nachhaltigkeit)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Verwaltungsfachangestellter</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-verwaltungsfachangestellter/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Robert Half Munich (All roles)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013471891-dede</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Randstad Germany (Munich, all roles)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Management-Assistenz (m/w/d)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>...nagement-Assistenz (m/w/d) in München | Randstad randstad Jobsuche...</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/management-assistenz-mwd_muenchen_c01310721/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Michael Page Germany (Nachhaltigkeit)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Facility Management</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/jobs/facility-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Michael Page Germany (Nachhaltigkeit)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sales Support &amp; Customer Service</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/jobs/sales-support-customer-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Amadeus Fire (Munich)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Backoffice</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>https://karriere.amadeus-fire.de/backoffice</t>
         </is>
       </c>
     </row>
@@ -1292,103 +1275,100 @@
       <c r="A23" s="3" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Robert Half Munich (Assistenz)</t>
+          <t>Manpower Germany (Munich)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Assistenz des Gesamtbetriebsrats ( w/m/d)</t>
+          <t>Teamassistenz (m/w/d) Empfang &amp; Recht</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>...tbetriebsrats ( w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+          <t>...nz (m/w/d) Empfang &amp; Recht in München | Manpower Germany (Deutsch)...</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistenz-des-gesamtbetriebsrats-wmd/06604-0013483434-dede</t>
+          <t>https://www.manpower.de/de/jobs/industry/teamassistenz-mwd-empfang-recht/35cf1dec-3f0c-4a32-a28e-dd12519a8612</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Robert Half Munich (Assistenz)</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>HR Assistent (w/m/d)</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>HR Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013482368-dede</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Facility Management</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/facility-management</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Robert Half Munich (Assistenz)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>HR-Assistent (w/m/d)</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>HR-Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013479384-dede</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sales Support &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/sales-support-customer-service</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Robert Half Munich (Assistenz)</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Sekretär der Führungsebene (w/m/d)</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>...Führungsebene (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sekretär-der-führungsebene-wmd/06604-0013471824-dede</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Amadeus Fire (Munich)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Backoffice</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://karriere.amadeus-fire.de/backoffice</t>
         </is>
       </c>
     </row>
@@ -1396,25 +1376,25 @@
       <c r="A27" s="3" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Robert Half Munich (All roles)</t>
+          <t>Manpower Germany (Munich)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kreditsachbearbeiter (w/m/d)</t>
+          <t>Sachbearbeiter Kredit- und Bürgschaftsmanagement (m/w/d)</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>...sachbearbeiter (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+          <t>...gschaftsmanagement (m/w/d) in München | Manpower Germany (Deutsch)...</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/kreditsachbearbeiter-wmd/06644-0013484134-dede</t>
+          <t>https://www.manpower.de/de/jobs/banken/sachbearbeiter-kredit-und-brgschaftsmanagement-mwd-/047b5a6f-dc78-459e-a025-62d811fa09f6</t>
         </is>
       </c>
     </row>
@@ -1422,23 +1402,173 @@
       <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>Manpower Germany (Munich)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Markensachbearbeiter / Trademark Paralegal (gn)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>...Trademark Paralegal (gn)  in München | Manpower Germany (Deutsch)...</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.manpower.de/de/jobs/industry/markensachbearbeiter-trademark-paralegal-gn-/69f6f741-003a-44e5-a5f5-56404a363040</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Assistenz des Gesamtbetriebsrats ( w/m/d)</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>...tbetriebsrats ( w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistenz-des-gesamtbetriebsrats-wmd/06604-0013483434-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013482368-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013479384-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sekretär der Führungsebene (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>...Führungsebene (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sekretär-der-führungsebene-wmd/06604-0013471824-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Robert Half Munich (All roles)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Kreditsachbearbeiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>...sachbearbeiter (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/kreditsachbearbeiter-wmd/06644-0013484134-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Technische Vertriebsassistenz (w/m/d)</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>...riebsassistenz (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>https://www.roberthalf.com/de/de/job/münchen-bayern/technische-vertriebsassistenz-wmd/06604-0013485530-dede</t>
         </is>
@@ -1499,442 +1629,425 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>5 C CarbonPlan 1 job 118</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/carbonplan</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr"/>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>6 F FirstCarbon Solutions (FCS), an ADEC Innovation 1 job 113</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/firstcarbon-solutions-fcs-an-adec-innovation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Climate Jobs</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://climate.jobs/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs?q=Sustainability</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>ESG &amp; Carbon</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Carbon</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs?q=Carbon</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Climate Policy</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs/category/advocacy-policy</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2 C Climate Collective Foundation 1 job 320</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/climate-collective-foundation</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>3 C Climate Action Reserve 2 jobs 164</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/climateactionreserve</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>4 G goodcarbon 3 jobs 127</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/goodcarbon-earth</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>7 C ClimateWorks Foundation 2 jobs 109</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/climateworks</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>EuroClimateJobs.com</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Carbon Capture and Storage (15)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>EuroClimateJobs.com</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Climate and Energy Analyst (27)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Remote Climate Jobs</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Remote Climate Jobs</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Remote Climate Jobs Newsletter</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Why climate.jobs?</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://climate.jobs/why-climate-jobs</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -469,6 +490,140 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CSR Jobs in München</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>...punkt Immobilien (m|w|d) MEAG MUNICH ERGO AssetManagement GmbH | M...</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nachhaltigkeit</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/nachhaltigkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -480,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,6 +678,824 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Planet A Foods</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Office Management &amp; HR - Werkstudent (f/m/d) Food Tech Startup | 14-20h/Woche</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://planetafoods.jobs.personio.de/job/2755621</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Assistant to the executive Board (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Garching</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2706851</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Community Manager (m/w/d) - Front Desk MakerSpace Garching</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Garching</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2709394</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Assistent Personalabteilung</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>...fentlichen Dienst mit Sitz in München, zum nächstmöglichen Zeitpunk...</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/deutschland/assistent-personalabteilung/06604-0013487193-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Export (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>...rbeiter Export (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-export-wmd/06640-0013462604-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013475955-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tempton Personaldienstleistungen</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>12.08.2026 Personalsachbearbeiter / kaufmännischer Mitarbeiterin Lohn und Gehalt / Bürokauffrau (m/w/d) München</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>...n auf LinkedIn Jetzt bewerben München , Vollzeit Personalsachbearbe...</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tempton.de/karriere-intern/jobs/personalsachbearbeiter-kaufmaennischer-mitarbeiterin-lohn-gehalt-buerokauffrau</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Buchhaltung</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-finanz-und-rechnungswesen/t-rechnungswesen/j-sachbearbeiter-buchhaltung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Auftragssachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-marketing-und-vertrieb/t-vertrieb-und-verkauf/j-auftragssachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz der Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz-der-geschaeftsfuehrung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bürokaufmann</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-buerokaufmann/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Empfangsmitarbeiter</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-empfangsmitarbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Personalsachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-personalwesen/j-personalsachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Projektassistenz</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektassistenz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Einkauf</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter-einkauf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Verwaltungsfachangestellter</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-verwaltungsfachangestellter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013471891-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Munich, all roles)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Management-Assistenz (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>...nagement-Assistenz (m/w/d) in München | Randstad randstad Jobsuche...</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/management-assistenz-mwd_muenchen_c01310721/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Facility Management</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/facility-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Sales Support &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/jobs/sales-support-customer-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Amadeus Fire (Munich)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Backoffice</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://karriere.amadeus-fire.de/backoffice</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz des Gesamtbetriebsrats ( w/m/d)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>...tbetriebsrats ( w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistenz-des-gesamtbetriebsrats-wmd/06604-0013483434-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistent-wmd/06604-0013490419-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013482368-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013479384-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Sekretär der Führungsebene (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>...Führungsebene (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sekretär-der-führungsebene-wmd/06604-0013471824-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Kreditsachbearbeiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>...sachbearbeiter (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/kreditsachbearbeiter-wmd/06644-0013484134-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Technische Vertriebsassistenz (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>...riebsassistenz (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/technische-vertriebsassistenz-wmd/06604-0013485530-dede</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -534,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -577,6 +1550,370 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>6 C CarbonPlan 1 job 194</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/carbonplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ESG &amp; Carbon</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1 C Climate Collective Foundation 1 job 515</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climate-collective-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>8 C Climate Action Reserve 2 jobs 139</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climateactionreserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>9 C Climate Equity Fund (Equity Fund) 1 job 127</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/equityfund</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Carbon Capture and Storage (19)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Climate and Energy Analyst (23)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Climate Policy</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/advocacy-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs Newsletter</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Why climate.jobs?</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/why-climate-jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -469,6 +490,114 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CSR Jobs in München</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>...punkt Immobilien (m|w|d) MEAG MUNICH ERGO AssetManagement GmbH | M...</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/csr-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NachhaltigeJobs.de (Munich)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Umwelt Jobs in München | NachhaltigeJobs Nachhaltige...</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nachhaltigejobs.de/umwelt-jobs/muenchen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -480,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,6 +652,772 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Planet A Foods</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Office Management &amp; HR - Werkstudent (f/m/d) Food Tech Startup | 14-20h/Woche</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://planetafoods.jobs.personio.de/job/2755621</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Assistant to the executive Board (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Garching</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2706851</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Community Manager (m/w/d) - Front Desk MakerSpace Garching</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Garching</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2709394</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Assistent Personalabteilung</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>...fentlichen Dienst mit Sitz in München, zum nächstmöglichen Zeitpunk...</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/deutschland/assistent-personalabteilung/06604-0013487193-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Export (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>...rbeiter Export (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-export-wmd/06640-0013462604-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013475955-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tempton Personaldienstleistungen</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>12.08.2026 Personalsachbearbeiter / kaufmännischer Mitarbeiterin Lohn und Gehalt / Bürokauffrau (m/w/d) München</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>...n auf LinkedIn Jetzt bewerben München , Vollzeit Personalsachbearbe...</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tempton.de/karriere-intern/jobs/personalsachbearbeiter-kaufmaennischer-mitarbeiterin-lohn-gehalt-buerokauffrau</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Buchhaltung</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-finanz-und-rechnungswesen/t-rechnungswesen/j-sachbearbeiter-buchhaltung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Auftragssachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-marketing-und-vertrieb/t-vertrieb-und-verkauf/j-auftragssachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz der Geschäftsführung</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-assistenz-der-geschaeftsfuehrung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bürokaufmann</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-buerokaufmann/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Empfangsmitarbeiter</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-empfangsmitarbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Personalsachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-personalwesen/j-personalsachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Projektassistenz</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektassistenz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-sachbearbeiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Einkauf</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-sachbearbeiter-einkauf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Nachhaltigkeit)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Verwaltungsfachangestellter</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/j-verwaltungsfachangestellter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sachbearbeiter Kreditorenbuchhaltung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>...renbuchhaltung (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sachbearbeiter-kreditorenbuchhaltung-wmd/06640-0013471891-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Germany (Munich, all roles)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Management-Assistenz (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>...nagement-Assistenz (m/w/d) in München | Randstad randstad Jobsuche...</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/management-assistenz-mwd_muenchen_c01310721/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Amadeus Fire (Munich)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Backoffice</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://karriere.amadeus-fire.de/backoffice</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Assistenz des Gesamtbetriebsrats ( w/m/d)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>...tbetriebsrats ( w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistenz-des-gesamtbetriebsrats-wmd/06604-0013483434-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/assistent-wmd/06604-0013490419-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>HR Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013482368-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>HR-Assistent (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/hr-assistent-wmd/06640-0013479384-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (Assistenz)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Sekretär der Führungsebene (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>...Führungsebene (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/sekretär-der-führungsebene-wmd/06604-0013471824-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Kreditsachbearbeiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>...sachbearbeiter (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/kreditsachbearbeiter-wmd/06644-0013484134-dede</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Robert Half Munich (All roles)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Technische Vertriebsassistenz (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>...riebsassistenz (w/m/d) Job in München, Bayern | Robert Half Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/de/de/job/münchen-bayern/technische-vertriebsassistenz-wmd/06604-0013485530-dede</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -534,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -577,6 +1472,370 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>ESG &amp; Carbon</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>6 C CarbonPlan 1 job 199</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/carbonplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>1 C Climate Collective Foundation 1 job 514</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climate-collective-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>8 C Climate Action Reserve 2 jobs 140</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climateactionreserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>9 C Climate Equity Fund (Equity Fund) 1 job 130</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/equityfund</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Carbon Capture and Storage (19)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Climate and Energy Analyst (23)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Climate Policy</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/advocacy-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs Newsletter</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Why climate.jobs?</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/why-climate-jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -469,6 +490,62 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -480,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,6 +600,768 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Intern / Working Student Online Training Translation (Korean speaking)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7886106003?gh_jid=7886106003</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>UVC Partners: Junior Value Creation Analyst - Intern or Working Student (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2750389</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant:in Accelerator Programme (RESPOND Energy &amp; Urban)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2709291</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>UVC Partners: Data &amp; AI - Master Thesis / Internship (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2769065</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Sales Intern (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2636858</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Siqens</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bachelorand / Masterand / Praktikant (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sfc.com/de/karriere/stellenanzeige/initiativbewerbung-bachelorand-masterand-praktikant-id94-104/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Finance &amp; Controlling (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2748370</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Unsolicited Application: Intern or Working Student for our Investment Team at UVC</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/1395193</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Praktikum beim BUND Naturschutz</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/praktikum</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NuuEnergy</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant/Werkstudent (m/w/d) People &amp; Culture</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://nuuenergy.jobs.personio.de/job/2761280</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>(Intern) Business Development (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2440947</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>(Intern) Entrepreneur in Residence (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2440935</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>(Intern) Founders Associate (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2440850</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM Company Partners: Praktikant_in (m/w/d) für Innovationsprojekte</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2468855</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>HAWE Hydraulik SE</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Schülerpraktikum</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>...&amp; Benefits Standorte Aschheim-München Barbing Freising Kaufbeuren S...</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://hawe.com/de-de/unternehmen/karriere/ausbildung/schuelerpraktikum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>BayernLB</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Traineeprogramm Vielfältige Einsatzbereiche, individuelle Entwicklung. Wir haben das passende Traineeprogramm für Dich!</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>...e moderne Kantine am Standort München Sportclub am Englischen Garte...</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/traineeprogramm/trainees_2024.jsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>The Mobility House</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Kreditorenbuchhaltung Praktikum/Werkstudium München</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2701912/werkstudent-mwd-kreditorenbuchhaltung</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>The Mobility House</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Werkstudent:in Projektmanagement Ladeinfrastruktur (m/w/d) Praktikum/Werkstudium München</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2717018/werkstudentin-projektmanagement-ladeinfrastruktur-mwd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Planet A Foods</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Praktikant:in (f/m/d)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://planetafoods.jobs.personio.de/job/1881523</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>BayernLB</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Praktikum und Abschlussarbeit</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>...finden in unserer Zentrale in München statt. Du kannst dich drei bi...</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/praktikum_und_abschlussarbeit_3/praktikum_und_werkstudenten.jsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Stadtwerke Muenchen</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Ausbildung | Schülerpraktikum</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>...hstarten? Bei den Stadtwerken München (SWM) arbeitest du nicht nur...</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.swm.de/karriere/berufseinsteiger/ausbildung</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>FINN</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Internship - B2B Sales (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/finn/fc5d1573-a0ef-4152-804f-099fb622b3b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>AMSilk</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Internship or Master’s Thesis in Downstream Process Development (6 months)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Neuried</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://amsilk.jobs.personio.de/job/1585005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Amadeus Fire (Munich)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Praktikum</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://karriere.amadeus-fire.de/praktikum</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>I.K. Hofmann / experts (Munich)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Interne Stellenangebote</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>...r Magdeburg Frankfurt Leipzig München Nürnberg Regensburg Zwickau F...</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://experts.jobs/bewerber/interne-stellenangebote/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Bavarian International School (BIS)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Open Positions at BAVARIAN INTERNATIONAL SCHOOL</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://bis.jobs.personio.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>AeroGround Flughafen München GmbH</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Initiativbewerbung für ein Hochschulpraktikum</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>...nschutz Newsletter ©Flughafen München GmbH powered by d.vinci</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://bewerben.munich-airport.de/de/jobs/382/intro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -534,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -577,6 +1416,344 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (1) On-site (29) Hybrid (46)...</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ESG &amp; Carbon</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (3) On-site (53) Hybrid (68)...</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (5) On-site (71) Hybrid (82)...</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2 C Climate Collective Foundation 1 job 489</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>...ganizational objectives. Work remotely (location not specified) Re...</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climate-collective-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>7 C Climate Action Reserve 2 jobs 146</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>...travel to project sites. Work remotely from United States Remote 🌍...</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climateactionreserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>8 C Climate Equity Fund (Equity Fund) 1 job 142</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>...nd fundraising outreach. Work remotely from United States Remote 📣...</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/equityfund</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Carbon Capture and Storage (19)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>...lace Hybrid (54) On-site (82) Remote (7) Jobs By Location Austria...</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Climate and Energy Analyst (24)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>...lace Hybrid (54) On-site (82) Remote (7) Jobs By Location Austria...</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Climate Policy</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (11) On-site (6) Hybrid (9) A...</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/advocacy-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Home | Remote Climate Jobs Remote Climate J...</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Home | Remote Climate Jobs Remote Climate J...</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs Newsletter</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Home | Remote Climate Jobs Remote Climate J...</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Why climate.jobs?</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>...limate since 2023 through the Remote Climate Jobs newsletter - whi...</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/why-climate-jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -491,56 +491,55 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Tanso</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Associate Sustainability Specialist (f/m/x)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://tanso.jobs.personio.de/job/2644410</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>BUND Naturschutz in Bayern</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
         </is>
@@ -601,762 +600,750 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Intern / Working Student Online Training Translation (Korean speaking)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7886106003?gh_jid=7886106003</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>UVC Partners: Junior Value Creation Analyst - Intern or Working Student (f/m/x)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2750389</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Praktikant:in Accelerator Programme (RESPOND Energy &amp; Urban)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2709291</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>UVC Partners: Data &amp; AI - Master Thesis / Internship (f/m/x)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2769065</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Tanso</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sales Intern (f/m/x)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://tanso.jobs.personio.de/job/2636858</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Siqens</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bachelorand / Masterand / Praktikant (m/w/d)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://www.sfc.com/de/karriere/stellenanzeige/initiativbewerbung-bachelorand-masterand-praktikant-id94-104/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Feldwerke</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Intern - Finance &amp; Controlling (m/w/d)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>München (Hybrid)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://feldwerke.jobs.personio.de/job/2748370</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2024-01-19</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Unsolicited Application: Intern or Working Student for our Investment Team at UVC</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/1395193</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>BUND Naturschutz in Bayern</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Praktikum beim BUND Naturschutz</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/praktikum</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>NuuEnergy</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Praktikant/Werkstudent (m/w/d) People &amp; Culture</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>München</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://nuuenergy.jobs.personio.de/job/2761280</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Feldwerke</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>(Intern) Business Development (m/w/d)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>München (Hybrid)</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://feldwerke.jobs.personio.de/job/2440947</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Feldwerke</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>(Intern) Entrepreneur in Residence (m/w/d)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>München (Hybrid)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://feldwerke.jobs.personio.de/job/2440935</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Feldwerke</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>(Intern) Founders Associate (m/w/d)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>München (Hybrid)</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://feldwerke.jobs.personio.de/job/2440850</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2025-12-19</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>UnternehmerTUM Company Partners: Praktikant_in (m/w/d) für Innovationsprojekte</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2468855</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HAWE Hydraulik SE</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Schülerpraktikum</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>...&amp; Benefits Standorte Aschheim-München Barbing Freising Kaufbeuren S...</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://hawe.com/de-de/unternehmen/karriere/ausbildung/schuelerpraktikum/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>BayernLB</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Traineeprogramm Vielfältige Einsatzbereiche, individuelle Entwicklung. Wir haben das passende Traineeprogramm für Dich!</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>...e moderne Kantine am Standort München Sportclub am Englischen Garte...</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/traineeprogramm/trainees_2024.jsp</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>The Mobility House</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Werkstudent (m/w/d) Kreditorenbuchhaltung Praktikum/Werkstudium München</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2701912/werkstudent-mwd-kreditorenbuchhaltung</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>The Mobility House</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Werkstudent:in Projektmanagement Ladeinfrastruktur (m/w/d) Praktikum/Werkstudium München</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2717018/werkstudentin-projektmanagement-ladeinfrastruktur-mwd</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2024-12-18</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Planet A Foods</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Marketing Praktikant:in (f/m/d)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://planetafoods.jobs.personio.de/job/1881523</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>BayernLB</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Praktikum und Abschlussarbeit</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>...finden in unserer Zentrale in München statt. Du kannst dich drei bi...</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/praktikum_und_abschlussarbeit_3/praktikum_und_werkstudenten.jsp</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Stadtwerke Muenchen</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ausbildung | Schülerpraktikum</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>...hstarten? Bei den Stadtwerken München (SWM) arbeitest du nicht nur...</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://www.swm.de/karriere/berufseinsteiger/ausbildung</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2024-08-27</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>FINN</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Internship - B2B Sales (m/w/d)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/finn/fc5d1573-a0ef-4152-804f-099fb622b3b8</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2024-06-03</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>AMSilk</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Internship or Master’s Thesis in Downstream Process Development (6 months)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Neuried</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>https://amsilk.jobs.personio.de/job/1585005</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Amadeus Fire (Munich)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Praktikum</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>...e Köln Leipzig Mainz Mannheim München Münster Nürnberg Stuttgart Fa...</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>https://karriere.amadeus-fire.de/praktikum</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>I.K. Hofmann / experts (Munich)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Interne Stellenangebote</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>...r Magdeburg Frankfurt Leipzig München Nürnberg Regensburg Zwickau F...</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>https://experts.jobs/bewerber/interne-stellenangebote/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Bavarian International School (BIS)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Open Positions at BAVARIAN INTERNATIONAL SCHOOL</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>https://bis.jobs.personio.de/</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>AeroGround Flughafen München GmbH</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Initiativbewerbung für ein Hochschulpraktikum</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>...nschutz Newsletter ©Flughafen München GmbH powered by d.vinci</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>https://bewerben.munich-airport.de/de/jobs/382/intro</t>
         </is>
@@ -1417,338 +1404,325 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>...k all → Search All work types Remote (1) On-site (29) Hybrid (46)...</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs?q=Sustainability</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr"/>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>ESG &amp; Carbon</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>...k all → Search All work types Remote (3) On-site (53) Hybrid (68)...</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Carbon</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>...k all → Search All work types Remote (5) On-site (71) Hybrid (82)...</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs?q=Carbon</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2 C Climate Collective Foundation 1 job 489</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>...ganizational objectives. Work remotely (location not specified) Re...</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/climate-collective-foundation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>7 C Climate Action Reserve 2 jobs 146</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>...travel to project sites. Work remotely from United States Remote 🌍...</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/climateactionreserve</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>8 C Climate Equity Fund (Equity Fund) 1 job 142</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>...nd fundraising outreach. Work remotely from United States Remote 📣...</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>https://climate.jobs/company/equityfund</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>EuroClimateJobs.com</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Carbon Capture and Storage (19)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>...lace Hybrid (54) On-site (82) Remote (7) Jobs By Location Austria...</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>EuroClimateJobs.com</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Climate and Energy Analyst (24)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>...lace Hybrid (54) On-site (82) Remote (7) Jobs By Location Austria...</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Climate Policy</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>...k all → Search All work types Remote (11) On-site (6) Hybrid (9) A...</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://climate.jobs/jobs/category/advocacy-policy</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Remote Climate Jobs</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Home | Remote Climate Jobs Remote Climate J...</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Remote Climate Jobs</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Home | Remote Climate Jobs Remote Climate J...</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Remote Climate Jobs Newsletter</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Home | Remote Climate Jobs Remote Climate J...</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>climate.jobs (remote)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Why climate.jobs?</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>...limate since 2023 through the Remote Climate Jobs newsletter - whi...</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://climate.jobs/why-climate-jobs</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1346,6 +1346,32 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>https://bewerben.munich-airport.de/de/jobs/382/intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Munich Re</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>2026 Fall Intern</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>...dern Insurance Group, Inc., a Munich Re company, is a widely recog...</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/amelia/2026-fall-intern/3342/43229230208</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -602,17 +602,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Intern / Working Student Online Training Translation (Korean speaking)</t>
+          <t>UVC Partners: Junior Value Creation Analyst - Intern or Working Student (f/m/x)</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -620,19 +620,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7886106003?gh_jid=7886106003</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2750389</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -642,11 +642,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UVC Partners: Junior Value Creation Analyst - Intern or Working Student (f/m/x)</t>
+          <t>Praktikant:in Accelerator Programme (RESPOND Energy &amp; Urban)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2750389</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2709291</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Praktikant:in Accelerator Programme (RESPOND Energy &amp; Urban)</t>
+          <t>UVC Partners: Data &amp; AI - Master Thesis / Internship (f/m/x)</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -685,24 +685,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2709291</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2769065</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>Tanso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UVC Partners: Data &amp; AI - Master Thesis / Internship (f/m/x)</t>
+          <t>Sales Intern (f/m/x)</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -710,29 +710,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2769065</t>
+          <t>https://tanso.jobs.personio.de/job/2636858</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tanso</t>
+          <t>Siqens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sales Intern (f/m/x)</t>
+          <t>Bachelorand / Masterand / Praktikant (m/w/d)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -745,79 +740,79 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://tanso.jobs.personio.de/job/2636858</t>
+          <t>https://www.sfc.com/de/karriere/stellenanzeige/initiativbewerbung-bachelorand-masterand-praktikant-id94-104/</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siqens</t>
+          <t>Feldwerke</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bachelorand / Masterand / Praktikant (m/w/d)</t>
+          <t>Intern - Finance &amp; Controlling (m/w/d)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München (Hybrid)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.sfc.com/de/karriere/stellenanzeige/initiativbewerbung-bachelorand-masterand-praktikant-id94-104/</t>
+          <t>https://feldwerke.jobs.personio.de/job/2748370</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Feldwerke</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Intern - Finance &amp; Controlling (m/w/d)</t>
+          <t>Unsolicited Application: Intern or Working Student for our Investment Team at UVC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>München (Hybrid)</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://feldwerke.jobs.personio.de/job/2748370</t>
+          <t>https://unternehmertum.jobs.personio.de/job/1395193</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024-01-19</t>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>BUND Naturschutz in Bayern</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unsolicited Application: Intern or Working Student for our Investment Team at UVC</t>
+          <t>Praktikum beim BUND Naturschutz</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -825,54 +820,59 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/1395193</t>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/praktikum</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BUND Naturschutz in Bayern</t>
+          <t>NuuEnergy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Praktikum beim BUND Naturschutz</t>
+          <t>Praktikant/Werkstudent (m/w/d) People &amp; Culture</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/praktikum</t>
+          <t>https://nuuenergy.jobs.personio.de/job/2761280</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NuuEnergy</t>
+          <t>Feldwerke</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Praktikant/Werkstudent (m/w/d) People &amp; Culture</t>
+          <t>(Intern) Business Development (m/w/d)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -880,12 +880,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>München</t>
+          <t>München (Hybrid)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://nuuenergy.jobs.personio.de/job/2761280</t>
+          <t>https://feldwerke.jobs.personio.de/job/2440947</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(Intern) Business Development (m/w/d)</t>
+          <t>(Intern) Entrepreneur in Residence (m/w/d)</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://feldwerke.jobs.personio.de/job/2440947</t>
+          <t>https://feldwerke.jobs.personio.de/job/2440935</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(Intern) Entrepreneur in Residence (m/w/d)</t>
+          <t>(Intern) Founders Associate (m/w/d)</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -945,54 +945,49 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://feldwerke.jobs.personio.de/job/2440935</t>
+          <t>https://feldwerke.jobs.personio.de/job/2440850</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Feldwerke</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(Intern) Founders Associate (m/w/d)</t>
+          <t>UnternehmerTUM Company Partners: Praktikant_in (m/w/d) für Innovationsprojekte</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>München (Hybrid)</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://feldwerke.jobs.personio.de/job/2440850</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2468855</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>HAWE Hydraulik SE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UnternehmerTUM Company Partners: Praktikant_in (m/w/d) für Innovationsprojekte</t>
+          <t>Schülerpraktikum</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1000,49 +995,49 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>...&amp; Benefits Standorte Aschheim-München Barbing Freising Kaufbeuren S...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2468855</t>
+          <t>https://hawe.com/de-de/unternehmen/karriere/ausbildung/schuelerpraktikum/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAWE Hydraulik SE</t>
+          <t>BayernLB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Schülerpraktikum</t>
+          <t>Traineeprogramm Vielfältige Einsatzbereiche, individuelle Entwicklung. Wir haben das passende Traineeprogramm für Dich!</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>...&amp; Benefits Standorte Aschheim-München Barbing Freising Kaufbeuren S...</t>
+          <t>...e moderne Kantine am Standort München Sportclub am Englischen Garte...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://hawe.com/de-de/unternehmen/karriere/ausbildung/schuelerpraktikum/</t>
+          <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/traineeprogramm/trainees_2024.jsp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>BayernLB</t>
+          <t>The Mobility House</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Traineeprogramm Vielfältige Einsatzbereiche, individuelle Entwicklung. Wir haben das passende Traineeprogramm für Dich!</t>
+          <t>Werkstudent (m/w/d) Kreditorenbuchhaltung Praktikum/Werkstudium München</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1050,12 +1045,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>...e moderne Kantine am Standort München Sportclub am Englischen Garte...</t>
+          <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/traineeprogramm/trainees_2024.jsp</t>
+          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2701912/werkstudent-mwd-kreditorenbuchhaltung</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1062,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Werkstudent (m/w/d) Kreditorenbuchhaltung Praktikum/Werkstudium München</t>
+          <t>Werkstudent:in Projektmanagement Ladeinfrastruktur (m/w/d) Praktikum/Werkstudium München</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1080,19 +1075,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2701912/werkstudent-mwd-kreditorenbuchhaltung</t>
+          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2717018/werkstudentin-projektmanagement-ladeinfrastruktur-mwd</t>
         </is>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Mobility House</t>
+          <t>Planet A Foods</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Werkstudent:in Projektmanagement Ladeinfrastruktur (m/w/d) Praktikum/Werkstudium München</t>
+          <t>Marketing Praktikant:in (f/m/d)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1100,42 +1100,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2717018/werkstudentin-projektmanagement-ladeinfrastruktur-mwd</t>
+          <t>https://planetafoods.jobs.personio.de/job/1881523</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Planet A Foods</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Marketing Praktikant:in (f/m/d)</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Munich Re</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://planetafoods.jobs.personio.de/job/1881523</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>...dern Insurance Group, Inc., a Munich Re company, is a widely recog...</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/amelia/intern/3342/43619098368</t>
         </is>
       </c>
     </row>
@@ -1350,26 +1346,25 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Munich Re</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2026 Fall Intern</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>...dern Insurance Group, Inc., a Munich Re company, is a widely recog...</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>https://careers.munichre.com/en/job/amelia/2026-fall-intern/3342/43229230208</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +83,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -470,6 +498,898 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Associate Sustainability Specialist (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2644410</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Spezialist Nachhaltige Beschaffung ESG-Compliance (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>...ehmer­über­lassung Arbeitsort München Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/11943-3DSEJM016JYCFB1E-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Praktikant Corporate Sustainability Reporting (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1572931-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tozero</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Hydrometallurgy Intern (Process Development &amp; R&amp;D) | Climate Tech Startup</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Munich HQ (Karlsfeld)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://tozero.jobs.personio.de/job/2083420</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Kreislaufwirtschaft, München)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Praktikant im Umweltmanagement (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1617917-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Dekarbonisierung, München)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ClimateTech Junior Customer Success &amp; Operations Assistant (m/f/d)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>...ereinstieg möglich Arbeitsort München Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002471683-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EY-Parthenon Praktikant  Corporate Real Estate, ESG (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>...eres ESG Real Estate Teams in München, Berlin, Düsseldorf, Köln, Fr...</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15548-1441932-3-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Oekobilanz, München)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Praktikant Produktnachhaltigkeit &amp; Ökobilanz (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1598828-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Praktikant Nachhaltigkeit Lieferantennetzwerk (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.09.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1603169-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Praktikant Corporate Responsibility / Nachhaltigkeit (Inhouse) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Vollzeit Benöt...</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15794-449073_32804-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Praktikant Lieferantenentwicklungskosten und Nachhaltigkeit Exterieur/Interieur (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1546765-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Professional General Accounting (m/w/d)- Schwerpunkt ESG-Reporting Finanzen</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort München Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003199093-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Referent*in für Klimaschutz und Energie (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/referentin-fuer-klimaschutz-und-energie-m/w/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaschutz, München)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Klimaschutzmanager / Klimaschutzmanagerin (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>...udwig-Maximilians-Universität München Das Wichtigste im Überblick B...</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/18818-dggzx1cyf9-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (CO2 Bilanzierung, München)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Manager Sustainability Services (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>...ibung für unser Team in Köln, München, Nürnberg oder Stuttgart Stel...</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002238931-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Energiewende, München)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Du stehst gerne unter Strom, dann bewirb dich bei uns als Elektroniker</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>...onat Beginn ab 01.09.2026 Ort München Angebotsart Ausbildung Anstel...</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003459133-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Energiewende, München)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Sachbearbeitung für Energie- und Umweltmanagement (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>...vsten Standorten im Landkreis München. Rund 11.300 Einwohnerinnen u...</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003506831-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeitsmanager, München)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent Sustainability &amp; DEI (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort München Anstellungsart Teilzeit (Vorm...</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15224-44375600-812-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeitsberater, München)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) im Bereich Nachhaltigkeit</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>...ginn ab 14.09.2026 Arbeitsort München Anstellungsart Teilzeit (Vorm...</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003484692-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, München)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>SAP Einsteiger*in Umweltinformatik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>...tellen in Berlin, Hamburg und München. Als SAP Servicepartner biete...</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002673964-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, München)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SAP Consultant Sustainability (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>...tellen in Berlin, Hamburg und München. Als SAP Servicepartner biete...</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1187603962-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent im Bereich ESG &amp; Risk (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Teilzeit (Vorm...</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12951-9ca2181f-ad39-4a52--S</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudium - Nachhaltigkeit &amp; ESG (m/w/x)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>...s Teams in Berg (im Süden von München) suchen wir Dich als Werkstud...</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003619017-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltingenieur, München)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Bauingenieur / Umweltingenieur / Architekt (w/m/d) für Nachhaltigkeitsberatung</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort München Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12951-1cc7ad8e-bc5b-4063--S</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltingenieur, München)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Bauingenieur / Umweltingenieur / Tiefbauingenieur (m/w/d) - Gewerbe- und Logistikbau</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>...rsonal­vermittlung Arbeitsort München Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003577900-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltiges Bauen, München)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Anlagenmechaniker (m/w/d) am Flughafen München für Sanitär-, Heizungs-, Lüftungs- und Klimatechnik</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>...chaniker (m/w/d) am Flughafen München für Sanitär-, Heizungs-, Lüft...</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003345620-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, München)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter:in Umweltschutz</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>...AG am Standort Nürnberg oder München. Deine Aufgaben: Du begleites...</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12456-1606367-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, München)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Polier m/w/d | Instandhaltung / Sanierung / Umweltschutz | Region Süddeutschland</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>...g. Arbeitsorte Karte anzeigen München Nürnberg, Mittelfranken Josef...</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1196406533-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, München)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Umweltschutzbeauftragter (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>...Merkmale Arbeitsort Poing bei München Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003402525-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, München)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Ausbildung zum Klimaschützer m/w/d</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>...rblick Besondere Merkmale Ort München Angebotsart Ausbildung Anstel...</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/14452-0060829532-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, München)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Umwelttechnolog*in - Abwasserbewirtschaftung (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>...(w/m/d) bei Landeshauptstadt München Personal- und Organisationsre...</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1207504574-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent Unternehmenskommunikation Nachhaltigkeit und Supply Chain (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1622423-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>SAP Consultant (m/w/d) Nachhaltigkeit diskrete Fertigung</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>...tellen in Berlin, Hamburg und München. Als SAP Servicepartner biete...</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002782357-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>SAP Consultant (m/w/d) Nachhaltigkeit diskrete Fertigung</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>...tellen in Berlin, Hamburg und München. Als SAP Servicepartner biete...</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002673930-S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -481,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,6 +1444,1004 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant:in Accelerator Programme (RESPOND Energy &amp; Urban)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2709291</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>BUND Naturschutz in Bayern</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Praktikum beim BUND Naturschutz</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bund-naturschutz.de/ueber-uns/stellenangebote/praktikum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tozero</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Hydrometallurgy Intern (Process Development &amp; R&amp;D) | Climate Tech Startup</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Munich HQ (Karlsfeld)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://tozero.jobs.personio.de/job/2083420</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant Corporate Sustainability Reporting (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1572931-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Founder's Associate Intern (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2605592</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Tanso</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Sales Intern (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://tanso.jobs.personio.de/job/2636858</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Oekobilanz, München)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant Produktnachhaltigkeit &amp; Ökobilanz (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1598828-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>UVC Partners: Data &amp; AI - Master Thesis / Internship (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2769065</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Finance &amp; Controlling (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2748370</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Greenforce</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Pflichtpraktikum im Produktmanagement (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>https://greenforce.jobs.personio.de/job/2765454</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>NuuEnergy</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant/Werkstudent (m/w/d) People &amp; Culture</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://nuuenergy.jobs.personio.de/job/2761280</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Greenforce</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Pflichtpraktikant Produktentwicklung vegane Lebensmittel (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>https://greenforce.jobs.personio.de/job/2765422</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Kreislaufwirtschaft, München)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant im Umweltmanagement (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1617917-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, München)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>EY-Parthenon Praktikant  Corporate Real Estate, ESG (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>...eres ESG Real Estate Teams in München, Berlin, Düsseldorf, Köln, Fr...</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15548-1441932-3-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>(Intern) Business Development (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2440947</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>(Intern) Entrepreneur in Residence (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2440935</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Feldwerke</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>(Intern) Founders Associate (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>München (Hybrid)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>https://feldwerke.jobs.personio.de/job/2440850</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant Nachhaltigkeit Lieferantennetzwerk (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.09.2026 Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1603169-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>The Mobility House</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Werkstudent (m/w/d) Kreditorenbuchhaltung Praktikum/Werkstudium München</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2701912/werkstudent-mwd-kreditorenbuchhaltung</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>The Mobility House</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Werkstudent:in Projektmanagement Ladeinfrastruktur (m/w/d) Praktikum/Werkstudium München</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>...eilzeit Praktikum/Werkstudium München Warum The Mobility House? Mit...</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mobilityhouse.com/de_de/unser-unternehmen/karriere/2717018/werkstudentin-projektmanagement-ladeinfrastruktur-mwd</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Tozero</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance System Engineering Intern</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Munich HQ (Karlsfeld)</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>https://tozero.jobs.personio.de/job/2739057</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Tozero</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Maintenance System Engineering Intern</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Plant (Gendorf)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>https://tozero.jobs.personio.de/job/2741059</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>AIRMO</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Business Development Intern, GCC &amp; wider MENA</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>https://airmo.jobs.personio.de/job/2722468</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant Corporate Responsibility / Nachhaltigkeit (Inhouse) (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Vollzeit Benöt...</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15794-449073_32804-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Stadtwerke Muenchen</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Ausbildung | Schülerpraktikum</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>...hstarten? Bei den Stadtwerken München (SWM) arbeitest du nicht nur...</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.swm.de/karriere/berufseinsteiger/ausbildung</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>BayernLB</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Traineeprogramm Vielfältige Einsatzbereiche, individuelle Entwicklung. Wir haben das passende Traineeprogramm für Dich!</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>...e moderne Kantine am Standort München Sportclub am Englischen Garte...</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/traineeprogramm/trainees_2024.jsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>BayernLB</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Praktikum und Abschlussarbeit</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>...finden in unserer Zentrale in München statt. Du kannst dich drei bi...</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bayernlb.de/internet/de/blb/resp/karriere_1/studenten_und_berufseinsteiger/praktikum_und_abschlussarbeit_3/praktikum_und_werkstudenten.jsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>FINN</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Internship - B2B Sales (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/finn/fc5d1573-a0ef-4152-804f-099fb622b3b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Unsolicited Application: Intern or Working Student for our Investment Team at UVC</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/1395193</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM Company Partners: Praktikant_in (m/w/d) für Innovationsprojekte</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2468855</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Planet A Foods</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Marketing Praktikant:in (f/m/d)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>https://planetafoods.jobs.personio.de/job/1881523</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>AMSilk</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Internship or Master’s Thesis in Downstream Process Development (6 months)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Neuried</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>https://amsilk.jobs.personio.de/job/1585005</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Greenforce</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Pflichtpraktikant im Backoffice (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>https://greenforce.jobs.personio.de/job/2648808</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Oceanloop</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Praktikum Aquakultur (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Kiel</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>https://oceanloop.jobs.personio.de/job/1110827</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, München)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Praktikant Lieferantenentwicklungskosten und Nachhaltigkeit Exterieur/Interieur (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort München Anstellungsart Vollzeit Befri...</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12462-1546765-1-S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -535,7 +2453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -578,6 +2496,344 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Carbon Capture and Storage (18)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>...lace Hybrid (55) On-site (83) Remote (7) Jobs By Location Austria...</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/carbon_capture_and_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>EuroClimateJobs.com</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Climate and Energy Analyst (23)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>...lace Hybrid (55) On-site (83) Remote (7) Jobs By Location Austria...</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.euroclimatejobs.com/jobs/climate_and_energy_analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (2) On-site (30) Hybrid (44)...</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ESG &amp; Carbon</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (3) On-site (55) Hybrid (66)...</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/esg-reporting-carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (5) On-site (72) Hybrid (81)...</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs?q=Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Climate Policy</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>...k all → Search All work types Remote (11) On-site (6) Hybrid (9) A...</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/jobs/category/advocacy-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2 C Climate Collective Foundation 1 job 480</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>...ganizational objectives. Work remotely (location not specified) Re...</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climate-collective-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>8 C Climate Equity Fund (Equity Fund) 1 job 148</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>...nd fundraising outreach. Work remotely from United States Remote 📣...</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/equityfund</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>9 C Climate Action Reserve 2 jobs 138</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>...travel to project sites. Work remotely from United States Remote 🌍...</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/company/climateactionreserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Home | Remote Climate Jobs Remote Climate J...</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=inline&amp;utm_campaign=upgrade&amp;utm_content=homepage-how-it-works</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Home | Remote Climate Jobs Remote Climate J...</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=faq&amp;utm_campaign=upgrade&amp;utm_content=homepage-faq-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Remote Climate Jobs Newsletter</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Home | Remote Climate Jobs Remote Climate J...</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://remoteclimatejobs.co?utm_source=climate.jobs&amp;utm_medium=footer&amp;utm_campaign=upgrade&amp;utm_content=footer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>climate.jobs (remote)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Why climate.jobs?</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>...limate since 2023 through the Remote Climate Jobs newsletter - whi...</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.jobs/why-climate-jobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -589,7 +2845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,6 +2888,1540 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, Berlin)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Sustainability &amp; Circularity Compliance Internship (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>...ginn ab 31.10.2026 Arbeitsort Berlin Berufsbezeichnung Sekretär/in...</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15158-2026278522-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, Berlin)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>EY-Parthenon Praktikant  Corporate Real Estate, ESG (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>...Real Estate Teams in München, Berlin, Düsseldorf, Köln, Frankfurt/...</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15548-1441932-3-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, Berlin)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Auditor / Technischer Spezialist (m/w/d) Nachhaltigkeit (ESG, RecyClass)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003618631-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Agora Energiewende</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Project Manager Budget and Finance for Europe’s Decarbonisation (f/m/d)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Berlin (assumed — single-office company)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.agora-energiewende.de/about-us/careers-at-agora-energiewende/open-positions/2753390</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Klima.Metrix</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Jobs at Klima.Metrix GmbH</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://join.com/companies/klimametrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Senatsverwaltung für Mobilität, Verkehr, Klimaschutz und Umwelt</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Umweltverträgliche Beschaffung</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>...Bau- und Sanierungsvorhaben - Berlin.de Senatsverwaltung für Mobil...</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.berlin.de/sen/uvk/klimaschutz/klimaschutz-in-der-umsetzung/projekte-monitoring/servicestelle-energetische-quartiersentwicklung/themen/oeffentliche-bauvorhaben/umweltvertraegliche-beschaffung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Senatsverwaltung für Mobilität, Verkehr, Klimaschutz und Umwelt</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>KliQ Klimafreundliches Quartier</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>...Klimafreundliches Quartier - Berlin.de Senatsverwaltung für Mobil...</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.berlin.de/sen/uvk/klimaschutz/klimaschutz-in-der-umsetzung/projekte-monitoring/servicestelle-energetische-quartiersentwicklung/praxisbeispiele/kliq-klimafreundliches-quartier/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Senatsverwaltung für Mobilität, Verkehr, Klimaschutz und Umwelt</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Koordinierungs­stelle für Kreislauf­wirtschaft, Energie­effizienz und Klimaschutz im Betrieb</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>...limaschutz im Betrieb (KEK) - Berlin.de Koordinierungsstelle für K...</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.berlin.de/service-energieeffizienz-kreislaufwirtschaft/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, Berlin)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Referent (m/w/d) Nachhaltigkeit und Compliance</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003609542-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (ESG, Berlin)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Manager Circular Economy</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1206839429-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimawandel, Berlin)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Business Development Manager Klimaschutz (d/m/w)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002665764-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimawandel, Berlin)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Sales Manager Klimaschutz (d/m/w)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002810968-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimawandel, Berlin)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Projektmanager Klimaschutzprojekte (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1202320505-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Referent (m/w/d) - Energie, Umwelt &amp; Klimaschutz</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>...ist wahlweise am Standort in Berlin oder Hannover möglich. Auf de...</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003555959-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Referent (m/w/d) - Energie, Umwelt &amp; Klimaschutz - unbefristete Festanstellung</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>...ist wahlweise am Standort in Berlin oder Hannover möglich. Auf de...</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003589406-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Referent (m/w/d) Nachhaltigkeit, Energie &amp; Umwelt - Berlin/Hannover</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>...altigkeit, Energie &amp; Umwelt - Berlin/Hannover | Jobsuche der BA Zu...</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003514237-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Referent (m/w/d) - Nachhaltigkeit, Energie &amp; Umwelt</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>...atz ist wahlweise am Standort Berlin oder Hannover möglich. Auf de...</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003461198-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Anlagenmechaniker SHK - Sanitär, Heizung, Klimatechnik</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1207265816-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeitsmanager, Berlin)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Klimamanager:in (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.12.2026 Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003521591-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Dekarbonisierung, Berlin)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Consultant Fördermittelberatung Innovation &amp; Nachhaltigkeit - Global Incentives Advisory (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>...ben Als Teil unserer Teams in Berlin, Hamburg oder Mannheim beräts...</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15548-1470011-2-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Dekarbonisierung, Berlin)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>EHS-Manager (w/m/d) Sifa</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15170-478430610-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Dekarbonisierung, Berlin)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Umweltschutzbeauftragter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15170-478430590-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaneutralitaet, Berlin)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Anlagenmechaniker Heizungs-, Klima- und Lüftungstechnik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003564564-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaneutralitaet, Berlin)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Obermonteur Luft- und Klimatechnik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>...Verstärken Sie unser Team in Berlin, Dortmund, Hamburg, Leipzig o...</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1149838546-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Klimaneutralitaet, Berlin)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Servicetechniker Heizung / Klima / Lüftung (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>...Verstärken Sie unser Team in Berlin, Dortmund, Hamburg, Leipzig o...</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1193010391-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Windenergie, Berlin)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Projektbearbeiter Umweltplanung (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>...em Standort in **Erkner **bei Berlin. Wir suchen erfahrene Umweltp...</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1205521409-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltingenieur, Berlin)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Energie- und Umweltingenieur (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>...ei FERCHAU GmbH Niederlassung Berlin Das Wichtigste im Überblick B...</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12265-444568_JB5223852-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltingenieur, Berlin)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Energie- und Umweltingenieur (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>...ei FERCHAU GmbH Niederlassung Berlin Das Wichtigste im Überblick B...</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12265-485275_JB5230174-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltingenieur, Berlin)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Umweltingenieur (m/w/d) mit dem Schwerpunkt Landespflege/ Landschaftsplanung</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Beginn ab...</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/13645-283963-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltingenieur, Berlin)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Umweltingenieur (m/w/d) mit dem Schwerpunkt Landespflege/ Landschaftsplanung, Berlin</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>...espflege/ Landschaftsplanung, Berlin | Jobsuche der BA Zur Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12811-2270823-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Kreislaufwirtschaft, Berlin)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Umweltmanager / Verantwortlicher für genehmigungspflichtige Anlagen (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002960921-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Erneuerbare Energien, Berlin)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Projektleiter Umweltplanung (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>...em Standort in **Erkner **bei Berlin. Wir suchen erfahrene Umweltp...</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1205520556-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Erneuerbare Energien, Berlin)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Anlagenmechaniker/in - Sanitär-, Heizungs- und Klimatechnik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1001533212-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Fachkraft Qualitäts- und Umweltmanagement m/w/d)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/14332-00002f29281001-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Werkstudent:in Umweltmanagement und Baukapazität im Projektmanagement</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>...rainee/Werkstudent Arbeitsort Berlin Anstellungsart Teilzeit (Vorm...</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12456-1620422-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Umweltexperte (m/w/d) mit dem Schwerpunkt Umweltmanagement, Landschaftsplanung bei der Ba..., Berlin</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>...schaftsplanung bei der Ba..., Berlin | Jobsuche der BA Zur Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12811-2223310-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>HSE Manager / Fachkraft Arbeitssicherheit &amp; Umweltmanagement (w/m/d) im Facility Management</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/17628-44379168-814-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>HSE Koordinator (m/w/d) Arbeitssicherheit &amp; Umweltschutz</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>...rsonal­vermittlung Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/20344-0066953510-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>SAP Einsteiger*in Umweltinformatik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>...nheim und Geschäftsstellen in Berlin, Hamburg und München. Als SAP...</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002673964-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>SAP Consultant Sustainability (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>...nheim und Geschäftsstellen in Berlin, Hamburg und München. Als SAP...</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1187603962-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltmanagement, Berlin)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Mitarbeiter/*in im Umwelt- und Genehmigungsmanagement (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>...r suchen wir für den Standort Berlin oder Potsdam eine/n Mitarbeit...</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003435621-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, Berlin)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Leiterin/ Leiter Einkaufsgrundsätze und Nachhaltigkeit (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>...nd Nachhaltigkeit (w/m/d) bei Berliner Verkehrsbetriebe (BVG) - Aö...</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12951-919d9ebc-d6b0-4e26--S</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, Berlin)</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>SAP Consultant (m/w/d) Nachhaltigkeit diskrete Fertigung</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>...nheim und Geschäftsstellen in Berlin, Hamburg und München. Als SAP...</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002782357-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, Berlin)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>SAP Consultant (m/w/d) Nachhaltigkeit diskrete Fertigung</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>...nheim und Geschäftsstellen in Berlin, Hamburg und München. Als SAP...</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002673930-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, Berlin)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Projektleiter im Bereich Simulation, Energie und Nachhaltigkeit (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Beginn ab...</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/13645-267145-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, Berlin)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Ingenieur:in / Techniker:in im Bereich Gebäudetechnik, Energie und Nachhaltigkeit (w/m/d)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort Berlin Beginn ab sofort Berufsbezeic...</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/13645-238482-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Nachhaltigkeit, Berlin)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Vertriebsmanager (m/w/d) für Nachhaltigkeitssoftware RTHINK</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>...ginn ab 01.10.2026 Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003617902-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Abfallwirtschaft, Berlin)</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Technische Sachbearbeitung im Bereich anlagenbezogener Umweltschutz mit Schwerpunkt Immissionsschutz</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>...z bei Bezirksamt Neukölln von Berlin Steuerungsdienst - SE Persona...</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/14795-68986_121891-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Abfallwirtschaft, Berlin)</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Bautechniker/Umwelttechniker als Projektbearbeiter/-leiter für Rückbau/Gebäudeschadstoffe (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>...ung unseres Teams am Standort Berlin-Brandenburg in Fredersdorf su...</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1003234378-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Recycling, Berlin)</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Bauleiter (m/w/d) Tiefbau / Umwelttechnik</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>...haften Bauunternehmen im Raum Berlin-Brandenburg. Durch unsere Arb...</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1207427011-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr"/>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Sachbearbeitung von Ordnungsaufgaben im Natur- und Umweltschutz (Fokus: Immissionsschutz)</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>...arlottenburg- Wilmersdorf von Berlin Das Wichtigste im Überblick S...</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/14795-68871_122888-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Fachkraft für Arbeitssicherheit, Brand- und Umweltschutz, St. Hedwig Krankenhaus Berlin</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>...chutz, St. Hedwig Krankenhaus Berlin | Jobsuche der BA Zur Jobsuch...</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12811-2309781-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Referent:in Umweltfachliche Bauüberwachung – Bodenschutz &amp; Abfall</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/12456-1624410-1-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Klimaschutzkoordinator (m/w/d) mit Schwerpunkt nachhaltiges Gebäudemanagement</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>...– 59.874,84 €/Jahr Arbeitsort Potsdam Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/14891-0066647848-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Projektleiter Umwelttechnik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>...Homeoffice möglich Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10000-1206804227-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr"/>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>EHS Manager (w/m/d) - Gefahrgut, Energiemanagement und Umwelt</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>...Besondere Merkmale Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/15170-459605006-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Umwelttechniker Ver- und Entsorgungsunternehmen (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>...e 57.742,20 €/Jahr Arbeitsort Königs Wusterhausen Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/14225-5522780d592dc5ac-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr"/>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>EHS Coordinator (d/m/w)</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>...Merkmale 1 €/Jahr Arbeitsort Berlin Angebotsart Arbeit Anstellung...</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/19287-44384727-817-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Bundesagentur für Arbeit (Umweltschutz, Berlin)</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Auditor für Umwelt- und Energiemanagement (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>...n unseren Standorten Leipzig, Berlin, Arnstadt oder Jena. Ihre Auf...</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.arbeitsagentur.de/jobsuche/jobdetail/10001-1002884070-S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
